--- a/data_group/contrast_PF_SF_prec.xlsx
+++ b/data_group/contrast_PF_SF_prec.xlsx
@@ -428,19 +428,19 @@
         </is>
       </c>
       <c r="D2">
-        <v>134.097181948047</v>
+        <v>132.9545222503924</v>
       </c>
       <c r="E2">
-        <v>23.36577647762294</v>
+        <v>17.92462440415505</v>
       </c>
       <c r="F2">
-        <v>702.0081503949148</v>
+        <v>662</v>
       </c>
       <c r="G2">
-        <v>-5.739042401457101</v>
+        <v>-7.417423051808698</v>
       </c>
       <c r="H2">
-        <v>8.499458257054711E-08</v>
+        <v>2.20282408949602E-12</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="D3">
-        <v>111.3302482107371</v>
+        <v>109.0769024885374</v>
       </c>
       <c r="E3">
-        <v>23.36577647762294</v>
+        <v>16.39824842413735</v>
       </c>
       <c r="F3">
-        <v>702.0081503985192</v>
+        <v>662</v>
       </c>
       <c r="G3">
-        <v>-4.764671455166765</v>
+        <v>-6.651741068148593</v>
       </c>
       <c r="H3">
-        <v>6.898964278298078E-06</v>
+        <v>1.821164258384918E-10</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -522,19 +522,19 @@
         </is>
       </c>
       <c r="D4">
-        <v>73.74881078003423</v>
+        <v>65.40670800565383</v>
       </c>
       <c r="E4">
-        <v>26.21097877443483</v>
+        <v>19.31029688390016</v>
       </c>
       <c r="F4">
-        <v>702.0559994361784</v>
+        <v>662</v>
       </c>
       <c r="G4">
-        <v>-2.813661077470558</v>
+        <v>-3.387141502738172</v>
       </c>
       <c r="H4">
-        <v>0.01007021394849623</v>
+        <v>0.0008976711462575898</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -569,19 +569,19 @@
         </is>
       </c>
       <c r="D5">
-        <v>176.042991883284</v>
+        <v>174.7646463225388</v>
       </c>
       <c r="E5">
-        <v>23.36577647762294</v>
+        <v>18.42080516001717</v>
       </c>
       <c r="F5">
-        <v>702.0081503982981</v>
+        <v>662</v>
       </c>
       <c r="G5">
-        <v>-7.534223912989916</v>
+        <v>-9.487351112201649</v>
       </c>
       <c r="H5">
-        <v>9.103721156749323E-13</v>
+        <v>1.990965622839781E-19</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -616,19 +616,19 @@
         </is>
       </c>
       <c r="D6">
-        <v>149.5449139813843</v>
+        <v>148.4990422313157</v>
       </c>
       <c r="E6">
-        <v>23.36577647762294</v>
+        <v>15.74316667517372</v>
       </c>
       <c r="F6">
-        <v>702.0081504049921</v>
+        <v>662</v>
       </c>
       <c r="G6">
-        <v>-6.400168816328498</v>
+        <v>-9.432603064889873</v>
       </c>
       <c r="H6">
-        <v>8.512294172181234E-10</v>
+        <v>1.990965622839781E-19</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -663,19 +663,19 @@
         </is>
       </c>
       <c r="D7">
-        <v>119.2073634760619</v>
+        <v>117.6794864549113</v>
       </c>
       <c r="E7">
-        <v>26.21097877443483</v>
+        <v>18.44687337876807</v>
       </c>
       <c r="F7">
-        <v>702.0559994373276</v>
+        <v>662</v>
       </c>
       <c r="G7">
-        <v>-4.547993590851026</v>
+        <v>-6.379373026453234</v>
       </c>
       <c r="H7">
-        <v>1.275837312651553E-05</v>
+        <v>6.680396543277345E-10</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -710,19 +710,19 @@
         </is>
       </c>
       <c r="D8">
-        <v>198.4773176532816</v>
+        <v>198.139337179867</v>
       </c>
       <c r="E8">
-        <v>23.36577647762296</v>
+        <v>19.82224742882243</v>
       </c>
       <c r="F8">
-        <v>702.0081504037749</v>
+        <v>662</v>
       </c>
       <c r="G8">
-        <v>-8.494360024515352</v>
+        <v>-9.995805868701021</v>
       </c>
       <c r="H8">
-        <v>7.11421521836913E-16</v>
+        <v>1.57795420176085E-21</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -757,19 +757,19 @@
         </is>
       </c>
       <c r="D9">
-        <v>168.0598659367791</v>
+        <v>166.611264684134</v>
       </c>
       <c r="E9">
-        <v>23.36577647762296</v>
+        <v>15.83767917472671</v>
       </c>
       <c r="F9">
-        <v>702.0081504053331</v>
+        <v>662</v>
       </c>
       <c r="G9">
-        <v>-7.192564993409372</v>
+        <v>-10.51992926779369</v>
       </c>
       <c r="H9">
-        <v>4.902651424027549E-12</v>
+        <v>2.922941759379829E-23</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -804,19 +804,19 @@
         </is>
       </c>
       <c r="D10">
-        <v>142.4165937138505</v>
+        <v>145.806778288069</v>
       </c>
       <c r="E10">
-        <v>26.21097877443485</v>
+        <v>18.80329151251065</v>
       </c>
       <c r="F10">
-        <v>702.0559994410141</v>
+        <v>662</v>
       </c>
       <c r="G10">
-        <v>-5.433471025231533</v>
+        <v>-7.754322065956241</v>
       </c>
       <c r="H10">
-        <v>1.52565678642959E-07</v>
+        <v>6.723790969041343E-14</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -851,19 +851,19 @@
         </is>
       </c>
       <c r="D11">
-        <v>189.5997868972756</v>
+        <v>187.6177014172058</v>
       </c>
       <c r="E11">
-        <v>23.36577647762295</v>
+        <v>18.84273317212763</v>
       </c>
       <c r="F11">
-        <v>702.0081504005987</v>
+        <v>662</v>
       </c>
       <c r="G11">
-        <v>-8.114422693328956</v>
+        <v>-9.95703222580957</v>
       </c>
       <c r="H11">
-        <v>1.310170966465424E-14</v>
+        <v>2.215990168199524E-21</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -898,19 +898,19 @@
         </is>
       </c>
       <c r="D12">
-        <v>167.2390264823648</v>
+        <v>165.7103807629795</v>
       </c>
       <c r="E12">
-        <v>23.36577647762294</v>
+        <v>15.88917022137776</v>
       </c>
       <c r="F12">
-        <v>702.0081504063977</v>
+        <v>662</v>
       </c>
       <c r="G12">
-        <v>-7.157435005103602</v>
+        <v>-10.42914000254261</v>
       </c>
       <c r="H12">
-        <v>6.227658855104629E-12</v>
+        <v>6.656855466015864E-23</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D13">
-        <v>146.6349884368212</v>
+        <v>152.0625003587289</v>
       </c>
       <c r="E13">
-        <v>26.21097877443483</v>
+        <v>20.31825435170968</v>
       </c>
       <c r="F13">
-        <v>702.0559994389977</v>
+        <v>662</v>
       </c>
       <c r="G13">
-        <v>-5.594411017563496</v>
+        <v>-7.484033703216909</v>
       </c>
       <c r="H13">
-        <v>6.347882012308575E-08</v>
+        <v>4.608309234597043E-13</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="D14">
-        <v>206.2581274604697</v>
+        <v>205.2030602015377</v>
       </c>
       <c r="E14">
-        <v>23.36577647762296</v>
+        <v>19.76751568936343</v>
       </c>
       <c r="F14">
-        <v>702.0081504055744</v>
+        <v>662</v>
       </c>
       <c r="G14">
-        <v>-8.827360291578579</v>
+        <v>-10.38082192148981</v>
       </c>
       <c r="H14">
-        <v>5.080088267102977E-17</v>
+        <v>1.029482700901162E-22</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1039,19 +1039,19 @@
         </is>
       </c>
       <c r="D15">
-        <v>161.7341537112116</v>
+        <v>156.3459235127347</v>
       </c>
       <c r="E15">
-        <v>23.36577647762296</v>
+        <v>15.92590281763042</v>
       </c>
       <c r="F15">
-        <v>702.0081504076134</v>
+        <v>662</v>
       </c>
       <c r="G15">
-        <v>-6.921839463203884</v>
+        <v>-9.817083860367109</v>
       </c>
       <c r="H15">
-        <v>3.020953022589706E-11</v>
+        <v>7.488720426019634E-21</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1086,19 +1086,19 @@
         </is>
       </c>
       <c r="D16">
-        <v>143.616111670028</v>
+        <v>150.9167500341701</v>
       </c>
       <c r="E16">
-        <v>26.21097877443484</v>
+        <v>19.98357486159562</v>
       </c>
       <c r="F16">
-        <v>702.0559994373866</v>
+        <v>662</v>
       </c>
       <c r="G16">
-        <v>-5.479234976532258</v>
+        <v>-7.552039666546421</v>
       </c>
       <c r="H16">
-        <v>1.191626178510569E-07</v>
+        <v>2.854133886062964E-13</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1133,19 +1133,19 @@
         </is>
       </c>
       <c r="D17">
-        <v>199.7795151679747</v>
+        <v>203.888499175552</v>
       </c>
       <c r="E17">
-        <v>23.36577647762296</v>
+        <v>23.42256841450941</v>
       </c>
       <c r="F17">
-        <v>702.0081504058124</v>
+        <v>662</v>
       </c>
       <c r="G17">
-        <v>-8.55009099994175</v>
+        <v>-8.70478828655062</v>
       </c>
       <c r="H17">
-        <v>4.59935414223405E-16</v>
+        <v>1.512374224624989E-16</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1180,19 +1180,19 @@
         </is>
       </c>
       <c r="D18">
-        <v>140.9734601601984</v>
+        <v>135.6090949044886</v>
       </c>
       <c r="E18">
-        <v>23.36577647762296</v>
+        <v>16.07686931470592</v>
       </c>
       <c r="F18">
-        <v>702.0081504076289</v>
+        <v>662</v>
       </c>
       <c r="G18">
-        <v>-6.033330854431757</v>
+        <v>-8.435043679831587</v>
       </c>
       <c r="H18">
-        <v>7.795940620186453E-09</v>
+        <v>6.226776191460615E-16</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1227,19 +1227,19 @@
         </is>
       </c>
       <c r="D19">
-        <v>115.3523301760635</v>
+        <v>125.1202789486543</v>
       </c>
       <c r="E19">
-        <v>26.21097877443484</v>
+        <v>21.40445496158779</v>
       </c>
       <c r="F19">
-        <v>702.0559994373932</v>
+        <v>662</v>
       </c>
       <c r="G19">
-        <v>-4.40091654603046</v>
+        <v>-5.845525110225599</v>
       </c>
       <c r="H19">
-        <v>2.49112355800079E-05</v>
+        <v>1.585789974402752E-08</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1274,19 +1274,19 @@
         </is>
       </c>
       <c r="D20">
-        <v>203.3489890434254</v>
+        <v>192.7777966541137</v>
       </c>
       <c r="E20">
-        <v>23.36577647762295</v>
+        <v>21.20738654075104</v>
       </c>
       <c r="F20">
-        <v>702.0081504006256</v>
+        <v>662</v>
       </c>
       <c r="G20">
-        <v>-8.702856044102353</v>
+        <v>-9.090125097860675</v>
       </c>
       <c r="H20">
-        <v>1.375531271354114E-16</v>
+        <v>6.81419773790208E-18</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1321,19 +1321,19 @@
         </is>
       </c>
       <c r="D21">
-        <v>99.61705714539971</v>
+        <v>93.39017875184716</v>
       </c>
       <c r="E21">
-        <v>23.36577647762295</v>
+        <v>18.77619561317764</v>
       </c>
       <c r="F21">
-        <v>702.0081504064658</v>
+        <v>662</v>
       </c>
       <c r="G21">
-        <v>-4.263374565822859</v>
+        <v>-4.97386055598523</v>
       </c>
       <c r="H21">
-        <v>4.57809557505706E-05</v>
+        <v>2.420601380376993E-06</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1368,19 +1368,19 @@
         </is>
       </c>
       <c r="D22">
-        <v>97.42206834117796</v>
+        <v>102.0619318636456</v>
       </c>
       <c r="E22">
-        <v>26.21097877443483</v>
+        <v>22.23006199284947</v>
       </c>
       <c r="F22">
-        <v>702.0559994388564</v>
+        <v>662</v>
       </c>
       <c r="G22">
-        <v>-3.716842059946256</v>
+        <v>-4.59116721745872</v>
       </c>
       <c r="H22">
-        <v>0.0002613469007438555</v>
+        <v>7.913274492868448E-06</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1415,19 +1415,19 @@
         </is>
       </c>
       <c r="D23">
-        <v>217.2246641272859</v>
+        <v>221.2614630964624</v>
       </c>
       <c r="E23">
-        <v>23.36577647762295</v>
+        <v>28.52492080228177</v>
       </c>
       <c r="F23">
-        <v>702.0081504039443</v>
+        <v>662</v>
       </c>
       <c r="G23">
-        <v>-9.296702137646426</v>
+        <v>-7.756777472937393</v>
       </c>
       <c r="H23">
-        <v>1.078090960193956E-18</v>
+        <v>1.98167391274893E-13</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1462,19 +1462,19 @@
         </is>
       </c>
       <c r="D24">
-        <v>137.8821793239508</v>
+        <v>113.9818908885969</v>
       </c>
       <c r="E24">
-        <v>23.36577647762296</v>
+        <v>22.88004247576947</v>
       </c>
       <c r="F24">
-        <v>702.0081504055275</v>
+        <v>662</v>
       </c>
       <c r="G24">
-        <v>-5.901031341971383</v>
+        <v>-4.98171675202555</v>
       </c>
       <c r="H24">
-        <v>1.686008596399075E-08</v>
+        <v>2.415708085885589E-06</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1509,19 +1509,19 @@
         </is>
       </c>
       <c r="D25">
-        <v>81.09245731714969</v>
+        <v>92.43720926581602</v>
       </c>
       <c r="E25">
-        <v>26.21097877443484</v>
+        <v>24.84573648758934</v>
       </c>
       <c r="F25">
-        <v>702.0559994412176</v>
+        <v>662</v>
       </c>
       <c r="G25">
-        <v>-3.09383552651777</v>
+        <v>-3.720445530442988</v>
       </c>
       <c r="H25">
-        <v>0.002465134082382202</v>
+        <v>0.0003236286157475357</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1556,19 +1556,19 @@
         </is>
       </c>
       <c r="D26">
-        <v>237.6577357334382</v>
+        <v>217.2014848994027</v>
       </c>
       <c r="E26">
-        <v>23.98877312693736</v>
+        <v>33.46061443039669</v>
       </c>
       <c r="F26">
-        <v>702.0158502486269</v>
+        <v>662</v>
       </c>
       <c r="G26">
-        <v>-9.907040033930233</v>
+        <v>-6.491258113362377</v>
       </c>
       <c r="H26">
-        <v>5.745700614560855E-21</v>
+        <v>1.001972616217119E-09</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1603,19 +1603,19 @@
         </is>
       </c>
       <c r="D27">
-        <v>110.3334778738633</v>
+        <v>75.04155402464485</v>
       </c>
       <c r="E27">
-        <v>23.36577647762293</v>
+        <v>22.05899572975412</v>
       </c>
       <c r="F27">
-        <v>702.008150404768</v>
+        <v>662</v>
       </c>
       <c r="G27">
-        <v>-4.72201204096633</v>
+        <v>-3.401857226139519</v>
       </c>
       <c r="H27">
-        <v>4.230585345368438E-06</v>
+        <v>0.0009747894757227325</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1650,19 +1650,19 @@
         </is>
       </c>
       <c r="D28">
-        <v>98.1100723568964</v>
+        <v>97.89872468167147</v>
       </c>
       <c r="E28">
-        <v>26.21097877443482</v>
+        <v>24.09873881152194</v>
       </c>
       <c r="F28">
-        <v>702.0559994374602</v>
+        <v>662</v>
       </c>
       <c r="G28">
-        <v>-3.743090756022785</v>
+        <v>-4.062400337517444</v>
       </c>
       <c r="H28">
-        <v>0.0002359710777378306</v>
+        <v>0.0001087880379626947</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1697,19 +1697,19 @@
         </is>
       </c>
       <c r="D29">
-        <v>139.5405353103845</v>
+        <v>108.5095706458884</v>
       </c>
       <c r="E29">
-        <v>25.65447853816975</v>
+        <v>51.10895441699666</v>
       </c>
       <c r="F29">
-        <v>702.0355397075119</v>
+        <v>662</v>
       </c>
       <c r="G29">
-        <v>-5.439227115950556</v>
+        <v>-2.123102925576633</v>
       </c>
       <c r="H29">
-        <v>2.21868995232735E-07</v>
+        <v>0.1023468955194407</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1719,11 +1719,6 @@
       <c r="J29" t="inlineStr">
         <is>
           <t>SF_early</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>*</t>
         </is>
       </c>
     </row>
@@ -1744,19 +1739,19 @@
         </is>
       </c>
       <c r="D30">
-        <v>40.6113983932933</v>
+        <v>2.334977458916214</v>
       </c>
       <c r="E30">
-        <v>23.36577647762294</v>
+        <v>30.1820867421689</v>
       </c>
       <c r="F30">
-        <v>702.008150399186</v>
+        <v>662</v>
       </c>
       <c r="G30">
-        <v>-1.738071851889289</v>
+        <v>-0.07736302260552118</v>
       </c>
       <c r="H30">
-        <v>0.09916396532355448</v>
+        <v>0.9383581319905702</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1786,19 +1781,19 @@
         </is>
       </c>
       <c r="D31">
-        <v>-35.63518042680543</v>
+        <v>-30.37646348944949</v>
       </c>
       <c r="E31">
-        <v>26.21097877443482</v>
+        <v>23.59514709146394</v>
       </c>
       <c r="F31">
-        <v>702.0559994370951</v>
+        <v>662</v>
       </c>
       <c r="G31">
-        <v>1.359551687614299</v>
+        <v>1.287403014344371</v>
       </c>
       <c r="H31">
-        <v>0.1744083265750608</v>
+        <v>0.2976056373801401</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1828,19 +1823,19 @@
         </is>
       </c>
       <c r="D32">
-        <v>490.713086424492</v>
+        <v>490.0435094884017</v>
       </c>
       <c r="E32">
-        <v>23.62645005562609</v>
+        <v>20.44291023836032</v>
       </c>
       <c r="F32">
-        <v>710.0077158273278</v>
+        <v>670</v>
       </c>
       <c r="G32">
-        <v>-20.76964949322296</v>
+        <v>-23.97131835803174</v>
       </c>
       <c r="H32">
-        <v>1.877716080985221E-74</v>
+        <v>2.144016637510905E-91</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1875,19 +1870,19 @@
         </is>
       </c>
       <c r="D33">
-        <v>458.7287609622372</v>
+        <v>459.0484107692975</v>
       </c>
       <c r="E33">
-        <v>23.62645005562609</v>
+        <v>21.12657359848023</v>
       </c>
       <c r="F33">
-        <v>710.0077158290774</v>
+        <v>670</v>
       </c>
       <c r="G33">
-        <v>-19.41589870176039</v>
+        <v>-21.72848373303278</v>
       </c>
       <c r="H33">
-        <v>3.314574647880302E-67</v>
+        <v>3.610040238412495E-79</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1922,19 +1917,19 @@
         </is>
       </c>
       <c r="D34">
-        <v>421.4142230615225</v>
+        <v>425.3412606783213</v>
       </c>
       <c r="E34">
-        <v>26.50260180485961</v>
+        <v>27.61961988167582</v>
       </c>
       <c r="F34">
-        <v>710.0587058871209</v>
+        <v>670</v>
       </c>
       <c r="G34">
-        <v>-15.90086234417372</v>
+        <v>-15.39996793947599</v>
       </c>
       <c r="H34">
-        <v>1.261012372754926E-48</v>
+        <v>9.781349746669465E-46</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1969,19 +1964,19 @@
         </is>
       </c>
       <c r="D35">
-        <v>493.6813460040865</v>
+        <v>492.6106019209948</v>
       </c>
       <c r="E35">
-        <v>23.62645005562607</v>
+        <v>18.52936855503706</v>
       </c>
       <c r="F35">
-        <v>710.0077158264597</v>
+        <v>670</v>
       </c>
       <c r="G35">
-        <v>-20.89528239925016</v>
+        <v>-26.58539606775119</v>
       </c>
       <c r="H35">
-        <v>3.686111125168981E-75</v>
+        <v>4.228235127312875E-106</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2016,19 +2011,19 @@
         </is>
       </c>
       <c r="D36">
-        <v>431.1331498215516</v>
+        <v>433.5729464278706</v>
       </c>
       <c r="E36">
-        <v>23.62645005562607</v>
+        <v>19.87947805841011</v>
       </c>
       <c r="F36">
-        <v>710.0077158267206</v>
+        <v>670</v>
       </c>
       <c r="G36">
-        <v>-18.24790219463748</v>
+        <v>-21.81007696248069</v>
       </c>
       <c r="H36">
-        <v>8.08477166549903E-61</v>
+        <v>1.272747841463233E-79</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2063,19 +2058,19 @@
         </is>
       </c>
       <c r="D37">
-        <v>350.5577882408032</v>
+        <v>352.3128603065792</v>
       </c>
       <c r="E37">
-        <v>26.50260180485959</v>
+        <v>22.93870835302355</v>
       </c>
       <c r="F37">
-        <v>710.0587058891801</v>
+        <v>670</v>
       </c>
       <c r="G37">
-        <v>-13.2272971092417</v>
+        <v>-15.35887962323479</v>
       </c>
       <c r="H37">
-        <v>1.462264442427724E-35</v>
+        <v>1.563431669696904E-45</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2110,19 +2105,19 @@
         </is>
       </c>
       <c r="D38">
-        <v>496.4043425217344</v>
+        <v>494.5122442345412</v>
       </c>
       <c r="E38">
-        <v>23.62645005562611</v>
+        <v>19.42992435236947</v>
       </c>
       <c r="F38">
-        <v>710.0077158256937</v>
+        <v>670</v>
       </c>
       <c r="G38">
-        <v>-21.01053443716683</v>
+        <v>-25.45106379553329</v>
       </c>
       <c r="H38">
-        <v>8.261416098597213E-76</v>
+        <v>1.024941687809122E-99</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2157,19 +2152,19 @@
         </is>
       </c>
       <c r="D39">
-        <v>412.3974738886153</v>
+        <v>416.8540360163077</v>
       </c>
       <c r="E39">
-        <v>23.62645005562611</v>
+        <v>19.06527037399841</v>
       </c>
       <c r="F39">
-        <v>710.0077158265367</v>
+        <v>670</v>
       </c>
       <c r="G39">
-        <v>-17.45490638321317</v>
+        <v>-21.86457510641032</v>
       </c>
       <c r="H39">
-        <v>1.45831335744074E-56</v>
+        <v>6.341173913675469E-80</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2204,19 +2199,19 @@
         </is>
       </c>
       <c r="D40">
-        <v>300.3096344572455</v>
+        <v>299.4711448418112</v>
       </c>
       <c r="E40">
-        <v>26.50260180485963</v>
+        <v>19.27040866397695</v>
       </c>
       <c r="F40">
-        <v>710.0587058882863</v>
+        <v>670</v>
       </c>
       <c r="G40">
-        <v>-11.33132651157969</v>
+        <v>-15.54046673652678</v>
       </c>
       <c r="H40">
-        <v>3.571555019253559E-27</v>
+        <v>1.958891037221969E-46</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2251,19 +2246,19 @@
         </is>
       </c>
       <c r="D41">
-        <v>460.276086661977</v>
+        <v>458.0535007161261</v>
       </c>
       <c r="E41">
-        <v>23.62645005562609</v>
+        <v>20.76403585779602</v>
       </c>
       <c r="F41">
-        <v>710.0077158252464</v>
+        <v>670</v>
       </c>
       <c r="G41">
-        <v>-19.48138994975138</v>
+        <v>-22.05994556420236</v>
       </c>
       <c r="H41">
-        <v>2.881444590043399E-67</v>
+        <v>1.041142485330162E-80</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2298,19 +2293,19 @@
         </is>
       </c>
       <c r="D42">
-        <v>370.4176301484321</v>
+        <v>375.932060062667</v>
       </c>
       <c r="E42">
-        <v>23.62645005562609</v>
+        <v>17.58146475221102</v>
       </c>
       <c r="F42">
-        <v>710.0077158272865</v>
+        <v>670</v>
       </c>
       <c r="G42">
-        <v>-15.67809083786693</v>
+        <v>-21.38229467003825</v>
       </c>
       <c r="H42">
-        <v>2.584454698178975E-47</v>
+        <v>2.98724728347947E-77</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2345,19 +2340,19 @@
         </is>
       </c>
       <c r="D43">
-        <v>239.9124320026882</v>
+        <v>237.3047662911972</v>
       </c>
       <c r="E43">
-        <v>26.50260180485961</v>
+        <v>16.96844096883898</v>
       </c>
       <c r="F43">
-        <v>710.0587058873022</v>
+        <v>670</v>
       </c>
       <c r="G43">
-        <v>-9.052410543280965</v>
+        <v>-13.9850659661065</v>
       </c>
       <c r="H43">
-        <v>2.656579953513978E-18</v>
+        <v>7.036688116055282E-39</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2392,19 +2387,19 @@
         </is>
       </c>
       <c r="D44">
-        <v>396.9727082724596</v>
+        <v>397.3732998363494</v>
       </c>
       <c r="E44">
-        <v>23.6264500556261</v>
+        <v>22.7005253048776</v>
       </c>
       <c r="F44">
-        <v>710.0077158254167</v>
+        <v>670</v>
       </c>
       <c r="G44">
-        <v>-16.8020463225676</v>
+        <v>-17.50502662380975</v>
       </c>
       <c r="H44">
-        <v>8.180041445545729E-53</v>
+        <v>2.642438962404794E-56</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2439,19 +2434,19 @@
         </is>
       </c>
       <c r="D45">
-        <v>316.0059470628935</v>
+        <v>320.4784733160767</v>
       </c>
       <c r="E45">
-        <v>23.6264500556261</v>
+        <v>14.66155004448809</v>
       </c>
       <c r="F45">
-        <v>710.0077158280532</v>
+        <v>670</v>
       </c>
       <c r="G45">
-        <v>-13.37509216657133</v>
+        <v>-21.85843054408551</v>
       </c>
       <c r="H45">
-        <v>4.509307230904757E-36</v>
+        <v>1.371893343847832E-79</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2486,19 +2481,19 @@
         </is>
       </c>
       <c r="D46">
-        <v>195.128736900298</v>
+        <v>194.3358533960837</v>
       </c>
       <c r="E46">
-        <v>26.50260180485962</v>
+        <v>15.01154860675094</v>
       </c>
       <c r="F46">
-        <v>710.0587058872625</v>
+        <v>670</v>
       </c>
       <c r="G46">
-        <v>-7.362625689999933</v>
+        <v>-12.94575652965529</v>
       </c>
       <c r="H46">
-        <v>7.510802329326875E-13</v>
+        <v>4.525549372866355E-34</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2533,19 +2528,19 @@
         </is>
       </c>
       <c r="D47">
-        <v>376.2779565777573</v>
+        <v>379.2871454212061</v>
       </c>
       <c r="E47">
-        <v>23.6264500556261</v>
+        <v>24.10191633350222</v>
       </c>
       <c r="F47">
-        <v>710.0077158254167</v>
+        <v>670</v>
       </c>
       <c r="G47">
-        <v>-15.92613175876395</v>
+        <v>-15.73680450022923</v>
       </c>
       <c r="H47">
-        <v>2.812417052394627E-48</v>
+        <v>3.070900922533437E-47</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2580,19 +2575,19 @@
         </is>
       </c>
       <c r="D48">
-        <v>285.6209668142047</v>
+        <v>290.4727537580801</v>
       </c>
       <c r="E48">
-        <v>23.6264500556261</v>
+        <v>15.25553864604955</v>
       </c>
       <c r="F48">
-        <v>710.0077158280533</v>
+        <v>670</v>
       </c>
       <c r="G48">
-        <v>-12.08903437214388</v>
+        <v>-19.04047837952275</v>
       </c>
       <c r="H48">
-        <v>2.996931619697906E-30</v>
+        <v>3.709021597424148E-64</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2627,19 +2622,19 @@
         </is>
       </c>
       <c r="D49">
-        <v>183.2226478603906</v>
+        <v>183.034646211201</v>
       </c>
       <c r="E49">
-        <v>26.50260180485962</v>
+        <v>15.35988711374698</v>
       </c>
       <c r="F49">
-        <v>710.0587058872276</v>
+        <v>670</v>
       </c>
       <c r="G49">
-        <v>-6.913383418332693</v>
+        <v>-11.91640569072845</v>
       </c>
       <c r="H49">
-        <v>1.583247053491639E-11</v>
+        <v>1.581485109913794E-29</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2674,19 +2669,19 @@
         </is>
       </c>
       <c r="D50">
-        <v>392.0635311400442</v>
+        <v>396.8999283289979</v>
       </c>
       <c r="E50">
-        <v>23.62645005562608</v>
+        <v>25.75370093737759</v>
       </c>
       <c r="F50">
-        <v>710.0077158252464</v>
+        <v>670</v>
       </c>
       <c r="G50">
-        <v>-16.59426321842555</v>
+        <v>-15.41137443873001</v>
       </c>
       <c r="H50">
-        <v>9.966141589932156E-52</v>
+        <v>1.287956722325523E-45</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2721,19 +2716,19 @@
         </is>
       </c>
       <c r="D51">
-        <v>301.7937863310584</v>
+        <v>304.1264201150648</v>
       </c>
       <c r="E51">
-        <v>23.62645005562608</v>
+        <v>15.6600754554478</v>
       </c>
       <c r="F51">
-        <v>710.0077158272866</v>
+        <v>670</v>
       </c>
       <c r="G51">
-        <v>-12.77355614662869</v>
+        <v>-19.42049519367199</v>
       </c>
       <c r="H51">
-        <v>2.646122343295817E-33</v>
+        <v>3.302115391501763E-66</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2768,19 +2763,19 @@
         </is>
       </c>
       <c r="D52">
-        <v>231.35329401987</v>
+        <v>231.8760033399506</v>
       </c>
       <c r="E52">
-        <v>26.5026018048596</v>
+        <v>15.77686125009406</v>
       </c>
       <c r="F52">
-        <v>710.0587058870599</v>
+        <v>670</v>
       </c>
       <c r="G52">
-        <v>-8.729455912417183</v>
+        <v>-14.69722016719695</v>
       </c>
       <c r="H52">
-        <v>3.632550475676591E-17</v>
+        <v>2.739520821747157E-42</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -2815,19 +2810,19 @@
         </is>
       </c>
       <c r="D53">
-        <v>428.9388919757068</v>
+        <v>436.1640980427349</v>
       </c>
       <c r="E53">
-        <v>23.62645005562609</v>
+        <v>29.8602791179299</v>
       </c>
       <c r="F53">
-        <v>710.0077158256935</v>
+        <v>670</v>
       </c>
       <c r="G53">
-        <v>-18.1550292560166</v>
+        <v>-14.60683258586273</v>
       </c>
       <c r="H53">
-        <v>5.137680019563696E-60</v>
+        <v>1.125538646252095E-41</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -2862,19 +2857,19 @@
         </is>
       </c>
       <c r="D54">
-        <v>322.9897359223612</v>
+        <v>326.1141905819382</v>
       </c>
       <c r="E54">
-        <v>23.62645005562609</v>
+        <v>18.55825456543186</v>
       </c>
       <c r="F54">
-        <v>710.0077158265367</v>
+        <v>670</v>
       </c>
       <c r="G54">
-        <v>-13.6706841341765</v>
+        <v>-17.57246024577039</v>
       </c>
       <c r="H54">
-        <v>1.846051661892005E-37</v>
+        <v>2.343579426851767E-56</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -2909,19 +2904,19 @@
         </is>
       </c>
       <c r="D55">
-        <v>258.8276198505621</v>
+        <v>257.9574346546636</v>
       </c>
       <c r="E55">
-        <v>26.50260180485962</v>
+        <v>19.85909885206678</v>
       </c>
       <c r="F55">
-        <v>710.0587058881116</v>
+        <v>670</v>
       </c>
       <c r="G55">
-        <v>-9.76612114374003</v>
+        <v>-12.98938267925573</v>
       </c>
       <c r="H55">
-        <v>6.351912738048686E-21</v>
+        <v>2.871583901348224E-34</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -2956,19 +2951,19 @@
         </is>
       </c>
       <c r="D56">
-        <v>441.3502308376514</v>
+        <v>453.3666371242831</v>
       </c>
       <c r="E56">
-        <v>23.62645005562609</v>
+        <v>34.11993803363052</v>
       </c>
       <c r="F56">
-        <v>710.00771582646</v>
+        <v>670</v>
       </c>
       <c r="G56">
-        <v>-18.68034468989361</v>
+        <v>-13.28744022563639</v>
       </c>
       <c r="H56">
-        <v>7.230549669255354E-63</v>
+        <v>3.760537176828879E-35</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3003,19 +2998,19 @@
         </is>
       </c>
       <c r="D57">
-        <v>324.8040758571975</v>
+        <v>330.3635293522697</v>
       </c>
       <c r="E57">
-        <v>23.62645005562609</v>
+        <v>25.27019026944989</v>
       </c>
       <c r="F57">
-        <v>710.0077158267209</v>
+        <v>670</v>
       </c>
       <c r="G57">
-        <v>-13.74747687834944</v>
+        <v>-13.07325057032352</v>
       </c>
       <c r="H57">
-        <v>7.995242492234941E-38</v>
+        <v>1.792035722562364E-34</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3050,19 +3045,19 @@
         </is>
       </c>
       <c r="D58">
-        <v>279.4960677817791</v>
+        <v>275.030029788528</v>
       </c>
       <c r="E58">
-        <v>26.50260180485961</v>
+        <v>22.84657362398671</v>
       </c>
       <c r="F58">
-        <v>710.0587058892819</v>
+        <v>670</v>
       </c>
       <c r="G58">
-        <v>-10.54598600694856</v>
+        <v>-12.03813028224823</v>
       </c>
       <c r="H58">
-        <v>5.907210972314578E-24</v>
+        <v>4.720434689390455E-30</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3097,19 +3092,19 @@
         </is>
       </c>
       <c r="D59">
-        <v>327.5757828977236</v>
+        <v>333.4546482843189</v>
       </c>
       <c r="E59">
-        <v>23.62645005562608</v>
+        <v>43.48206259483987</v>
       </c>
       <c r="F59">
-        <v>710.0077158273284</v>
+        <v>670</v>
       </c>
       <c r="G59">
-        <v>-13.86479061079763</v>
+        <v>-7.668786354304425</v>
       </c>
       <c r="H59">
-        <v>4.430549042079488E-38</v>
+        <v>3.677914014402264E-13</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3144,19 +3139,19 @@
         </is>
       </c>
       <c r="D60">
-        <v>199.9373330036807</v>
+        <v>204.6397457422797</v>
       </c>
       <c r="E60">
-        <v>23.62645005562608</v>
+        <v>30.75903227711476</v>
       </c>
       <c r="F60">
-        <v>710.0077158290774</v>
+        <v>670</v>
       </c>
       <c r="G60">
-        <v>-8.462436486774296</v>
+        <v>-6.652996879051202</v>
       </c>
       <c r="H60">
-        <v>4.478045611353017E-16</v>
+        <v>1.791403918525469E-10</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3191,19 +3186,19 @@
         </is>
       </c>
       <c r="D61">
-        <v>135.7539413538798</v>
+        <v>124.0444193380708</v>
       </c>
       <c r="E61">
-        <v>26.50260180485961</v>
+        <v>33.24491334980788</v>
       </c>
       <c r="F61">
-        <v>710.0587058875983</v>
+        <v>670</v>
       </c>
       <c r="G61">
-        <v>-5.122287326861148</v>
+        <v>-3.73123003909973</v>
       </c>
       <c r="H61">
-        <v>4.671744037551307E-07</v>
+        <v>0.0003100552314677493</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3238,19 +3233,19 @@
         </is>
       </c>
       <c r="D62">
-        <v>102.6641122944042</v>
+        <v>102.4129754544411</v>
       </c>
       <c r="E62">
-        <v>15.4722551405371</v>
+        <v>9.527155272647793</v>
       </c>
       <c r="F62">
-        <v>710.002902011585</v>
+        <v>670</v>
       </c>
       <c r="G62">
-        <v>-6.635368364979038</v>
+        <v>-10.7495860541358</v>
       </c>
       <c r="H62">
-        <v>1.284749718084235E-10</v>
+        <v>1.13098012091761E-24</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3285,19 +3280,19 @@
         </is>
       </c>
       <c r="D63">
-        <v>121.020236077711</v>
+        <v>122.0806116576553</v>
       </c>
       <c r="E63">
-        <v>15.4722551405371</v>
+        <v>10.0406327147089</v>
       </c>
       <c r="F63">
-        <v>710.0029020094561</v>
+        <v>670</v>
       </c>
       <c r="G63">
-        <v>-7.821758042280448</v>
+        <v>-12.15865724067517</v>
       </c>
       <c r="H63">
-        <v>5.664721909095306E-14</v>
+        <v>2.122484335514358E-30</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3332,19 +3327,19 @@
         </is>
       </c>
       <c r="D64">
-        <v>159.1937142518946</v>
+        <v>150.6621666089473</v>
       </c>
       <c r="E64">
-        <v>17.35584111099147</v>
+        <v>11.86350695453081</v>
       </c>
       <c r="F64">
-        <v>710.0408063560244</v>
+        <v>670</v>
       </c>
       <c r="G64">
-        <v>-9.172342223799062</v>
+        <v>-12.69963149904908</v>
       </c>
       <c r="H64">
-        <v>2.961761329708108E-18</v>
+        <v>1.737483319670382E-32</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3379,19 +3374,19 @@
         </is>
       </c>
       <c r="D65">
-        <v>102.0022153212962</v>
+        <v>102.4187027846321</v>
       </c>
       <c r="E65">
-        <v>15.47225514053709</v>
+        <v>9.420362997488029</v>
       </c>
       <c r="F65">
-        <v>710.0029020106508</v>
+        <v>670</v>
       </c>
       <c r="G65">
-        <v>-6.592588759349748</v>
+        <v>-10.87205480425143</v>
       </c>
       <c r="H65">
-        <v>1.686934278410233E-10</v>
+        <v>3.628709281830518E-25</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3426,19 +3421,19 @@
         </is>
       </c>
       <c r="D66">
-        <v>122.1411106173025</v>
+        <v>122.0012029333599</v>
       </c>
       <c r="E66">
-        <v>15.47225514053709</v>
+        <v>9.069316608133576</v>
       </c>
       <c r="F66">
-        <v>710.0029020094718</v>
+        <v>670</v>
       </c>
       <c r="G66">
-        <v>-7.894202203096722</v>
+        <v>-13.45208334925107</v>
       </c>
       <c r="H66">
-        <v>3.327879866290646E-14</v>
+        <v>3.276492018587775E-36</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3473,19 +3468,19 @@
         </is>
       </c>
       <c r="D67">
-        <v>173.3545872600699</v>
+        <v>164.2200845899285</v>
       </c>
       <c r="E67">
-        <v>17.35584111099146</v>
+        <v>11.87649348499265</v>
       </c>
       <c r="F67">
-        <v>710.0408063562846</v>
+        <v>670</v>
       </c>
       <c r="G67">
-        <v>-9.988256181389236</v>
+        <v>-13.82732073212012</v>
       </c>
       <c r="H67">
-        <v>2.715844540983023E-21</v>
+        <v>1.168312510276062E-37</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3520,19 +3515,19 @@
         </is>
       </c>
       <c r="D68">
-        <v>104.1575902221316</v>
+        <v>107.5745910875741</v>
       </c>
       <c r="E68">
-        <v>15.47225514053711</v>
+        <v>10.1924398775901</v>
       </c>
       <c r="F68">
-        <v>710.0029020109695</v>
+        <v>670</v>
       </c>
       <c r="G68">
-        <v>-6.731894560686248</v>
+        <v>-10.55435130150692</v>
       </c>
       <c r="H68">
-        <v>6.911510757552093E-11</v>
+        <v>6.799754065386813E-24</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3567,19 +3562,19 @@
         </is>
       </c>
       <c r="D69">
-        <v>124.8387195037876</v>
+        <v>125.1454578485941</v>
       </c>
       <c r="E69">
-        <v>15.47225514053711</v>
+        <v>9.009249887569153</v>
       </c>
       <c r="F69">
-        <v>710.0029020092218</v>
+        <v>670</v>
       </c>
       <c r="G69">
-        <v>-8.068553573467886</v>
+        <v>-13.89077441633273</v>
       </c>
       <c r="H69">
-        <v>9.102324248673747E-15</v>
+        <v>2.938838912235353E-38</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3614,19 +3609,19 @@
         </is>
       </c>
       <c r="D70">
-        <v>174.6378073382661</v>
+        <v>163.3990483020801</v>
       </c>
       <c r="E70">
-        <v>17.35584111099148</v>
+        <v>11.5332433232895</v>
       </c>
       <c r="F70">
-        <v>710.040806355453</v>
+        <v>670</v>
       </c>
       <c r="G70">
-        <v>-10.06219210129019</v>
+        <v>-14.16765810985037</v>
       </c>
       <c r="H70">
-        <v>1.40982869617127E-21</v>
+        <v>2.875632690007928E-39</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3661,19 +3656,19 @@
         </is>
       </c>
       <c r="D71">
-        <v>113.7263989228193</v>
+        <v>122.0452980615721</v>
       </c>
       <c r="E71">
-        <v>15.4722551405371</v>
+        <v>12.36272063313275</v>
       </c>
       <c r="F71">
-        <v>710.0029020099815</v>
+        <v>670</v>
       </c>
       <c r="G71">
-        <v>-7.350344076530749</v>
+        <v>-9.872042059616248</v>
       </c>
       <c r="H71">
-        <v>1.090854213714628E-12</v>
+        <v>2.98859164695594E-21</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -3708,19 +3703,19 @@
         </is>
       </c>
       <c r="D72">
-        <v>132.5282111522073</v>
+        <v>134.5983050337354</v>
       </c>
       <c r="E72">
-        <v>15.4722551405371</v>
+        <v>8.720801553840055</v>
       </c>
       <c r="F72">
-        <v>710.0029020094076</v>
+        <v>670</v>
       </c>
       <c r="G72">
-        <v>-8.565539408989268</v>
+        <v>-15.43416671079591</v>
       </c>
       <c r="H72">
-        <v>1.997759163232108E-16</v>
+        <v>1.985170444815486E-45</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -3755,19 +3750,19 @@
         </is>
       </c>
       <c r="D73">
-        <v>180.0121914757774</v>
+        <v>169.3467746381757</v>
       </c>
       <c r="E73">
-        <v>17.35584111099147</v>
+        <v>11.53802891516013</v>
       </c>
       <c r="F73">
-        <v>710.0408063563601</v>
+        <v>670</v>
       </c>
       <c r="G73">
-        <v>-10.3718506250772</v>
+        <v>-14.67727077851801</v>
       </c>
       <c r="H73">
-        <v>8.710742317531806E-23</v>
+        <v>5.134100180015522E-42</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -3802,19 +3797,19 @@
         </is>
       </c>
       <c r="D74">
-        <v>99.66442575690502</v>
+        <v>109.0993143198595</v>
       </c>
       <c r="E74">
-        <v>15.47225514053711</v>
+        <v>11.74044145503396</v>
       </c>
       <c r="F74">
-        <v>710.0029020103356</v>
+        <v>670</v>
       </c>
       <c r="G74">
-        <v>-6.441493166421844</v>
+        <v>-9.292607500127771</v>
       </c>
       <c r="H74">
-        <v>4.361957369280071E-10</v>
+        <v>4.154734759649168E-19</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -3849,19 +3844,19 @@
         </is>
       </c>
       <c r="D75">
-        <v>127.3670062502422</v>
+        <v>130.9935478087788</v>
       </c>
       <c r="E75">
-        <v>15.47225514053711</v>
+        <v>9.099987788187136</v>
       </c>
       <c r="F75">
-        <v>710.0029020095981</v>
+        <v>670</v>
       </c>
       <c r="G75">
-        <v>-8.231961345863686</v>
+        <v>-14.39491468096517</v>
       </c>
       <c r="H75">
-        <v>2.645585696499983E-15</v>
+        <v>1.180076189370945E-40</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -3896,19 +3891,19 @@
         </is>
       </c>
       <c r="D76">
-        <v>181.588144024067</v>
+        <v>176.9577913734527</v>
       </c>
       <c r="E76">
-        <v>17.35584111099147</v>
+        <v>9.900055294856195</v>
       </c>
       <c r="F76">
-        <v>710.0408063549162</v>
+        <v>670</v>
       </c>
       <c r="G76">
-        <v>-10.46265305511855</v>
+        <v>-17.87442454643615</v>
       </c>
       <c r="H76">
-        <v>3.806239954245367E-23</v>
+        <v>6.060598271995383E-58</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -3943,19 +3938,19 @@
         </is>
       </c>
       <c r="D77">
-        <v>99.96075525096396</v>
+        <v>119.7022244104185</v>
       </c>
       <c r="E77">
-        <v>15.47225514053711</v>
+        <v>15.32824185206516</v>
       </c>
       <c r="F77">
-        <v>710.0029020103359</v>
+        <v>670</v>
       </c>
       <c r="G77">
-        <v>-6.460645480765635</v>
+        <v>-7.809259898537618</v>
       </c>
       <c r="H77">
-        <v>3.871075017507734E-10</v>
+        <v>4.447311530724286E-14</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -3990,19 +3985,19 @@
         </is>
       </c>
       <c r="D78">
-        <v>118.875515175328</v>
+        <v>122.1133363296581</v>
       </c>
       <c r="E78">
-        <v>15.47225514053711</v>
+        <v>8.644443110711526</v>
       </c>
       <c r="F78">
-        <v>710.0029020095981</v>
+        <v>670</v>
       </c>
       <c r="G78">
-        <v>-7.683140828247828</v>
+        <v>-14.126223605815</v>
       </c>
       <c r="H78">
-        <v>1.550163238208594E-13</v>
+        <v>2.263021809833686E-39</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -4037,19 +4032,19 @@
         </is>
       </c>
       <c r="D79">
-        <v>166.5304022862092</v>
+        <v>157.16776171568</v>
       </c>
       <c r="E79">
-        <v>17.35584111099148</v>
+        <v>9.654232428584056</v>
       </c>
       <c r="F79">
-        <v>710.0408063547294</v>
+        <v>670</v>
       </c>
       <c r="G79">
-        <v>-9.595063772550052</v>
+        <v>-16.27967452392599</v>
       </c>
       <c r="H79">
-        <v>8.355808749500089E-20</v>
+        <v>1.116561901891775E-49</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -4084,19 +4079,19 @@
         </is>
       </c>
       <c r="D80">
-        <v>116.265727544398</v>
+        <v>133.6791048373819</v>
       </c>
       <c r="E80">
-        <v>15.4722551405371</v>
+        <v>16.28414871314455</v>
       </c>
       <c r="F80">
-        <v>710.0029020099821</v>
+        <v>670</v>
       </c>
       <c r="G80">
-        <v>-7.51446550540544</v>
+        <v>-8.209155246136767</v>
       </c>
       <c r="H80">
-        <v>3.44884118506706E-13</v>
+        <v>2.288514541682468E-15</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -4131,19 +4126,19 @@
         </is>
       </c>
       <c r="D81">
-        <v>156.4761083635255</v>
+        <v>161.6214608545791</v>
       </c>
       <c r="E81">
-        <v>15.4722551405371</v>
+        <v>9.232998855809765</v>
       </c>
       <c r="F81">
-        <v>710.0029020094076</v>
+        <v>670</v>
       </c>
       <c r="G81">
-        <v>-10.11333557663228</v>
+        <v>-17.50476344453141</v>
       </c>
       <c r="H81">
-        <v>4.47042846715754E-22</v>
+        <v>5.301664973820743E-56</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4178,19 +4173,19 @@
         </is>
       </c>
       <c r="D82">
-        <v>202.7734932717194</v>
+        <v>193.9734513481177</v>
       </c>
       <c r="E82">
-        <v>17.35584111099146</v>
+        <v>12.06005468684662</v>
       </c>
       <c r="F82">
-        <v>710.0408063564124</v>
+        <v>670</v>
       </c>
       <c r="G82">
-        <v>-11.68329970152256</v>
+        <v>-16.08396117470977</v>
       </c>
       <c r="H82">
-        <v>3.439881441265153E-28</v>
+        <v>5.489109833441815E-49</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -4225,19 +4220,19 @@
         </is>
       </c>
       <c r="D83">
-        <v>130.4866496731357</v>
+        <v>150.8957893615983</v>
       </c>
       <c r="E83">
-        <v>15.4722551405371</v>
+        <v>17.15426386694205</v>
       </c>
       <c r="F83">
-        <v>710.0029020109695</v>
+        <v>670</v>
       </c>
       <c r="G83">
-        <v>-8.433589576173834</v>
+        <v>-8.796401322261882</v>
       </c>
       <c r="H83">
-        <v>3.736637288403903E-16</v>
+        <v>2.377504633784666E-17</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -4272,19 +4267,19 @@
         </is>
       </c>
       <c r="D84">
-        <v>168.4955433745698</v>
+        <v>171.0933002870033</v>
       </c>
       <c r="E84">
-        <v>15.4722551405371</v>
+        <v>9.590867808168802</v>
       </c>
       <c r="F84">
-        <v>710.0029020092218</v>
+        <v>670</v>
       </c>
       <c r="G84">
-        <v>-10.89017352959192</v>
+        <v>-17.83918866458346</v>
       </c>
       <c r="H84">
-        <v>3.604633181933111E-25</v>
+        <v>9.294698790492077E-58</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -4319,19 +4314,19 @@
         </is>
       </c>
       <c r="D85">
-        <v>216.0601695515107</v>
+        <v>214.5033156763947</v>
       </c>
       <c r="E85">
-        <v>17.35584111099147</v>
+        <v>15.08227115553536</v>
       </c>
       <c r="F85">
-        <v>710.0408063554382</v>
+        <v>670</v>
       </c>
       <c r="G85">
-        <v>-12.44884463794034</v>
+        <v>-14.22221583635098</v>
       </c>
       <c r="H85">
-        <v>1.532653451038896E-31</v>
+        <v>7.904298520522365E-40</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -4366,19 +4361,19 @@
         </is>
       </c>
       <c r="D86">
-        <v>138.566135325876</v>
+        <v>166.8575723127036</v>
       </c>
       <c r="E86">
-        <v>15.4722551405371</v>
+        <v>20.68931360702586</v>
       </c>
       <c r="F86">
-        <v>710.002902010651</v>
+        <v>670</v>
       </c>
       <c r="G86">
-        <v>-8.955781433750701</v>
+        <v>-8.064915805425304</v>
       </c>
       <c r="H86">
-        <v>5.856045725667468E-18</v>
+        <v>6.764289288152257E-15</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -4413,19 +4408,19 @@
         </is>
       </c>
       <c r="D87">
-        <v>175.9263820548525</v>
+        <v>184.0265437068146</v>
       </c>
       <c r="E87">
-        <v>15.4722551405371</v>
+        <v>10.60524601230884</v>
       </c>
       <c r="F87">
-        <v>710.0029020094717</v>
+        <v>670</v>
       </c>
       <c r="G87">
-        <v>-11.37044215318863</v>
+        <v>-17.35240686479375</v>
       </c>
       <c r="H87">
-        <v>3.669922682818935E-27</v>
+        <v>3.31490333228383E-55</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -4460,19 +4455,19 @@
         </is>
       </c>
       <c r="D88">
-        <v>226.7053730270434</v>
+        <v>217.5499803546323</v>
       </c>
       <c r="E88">
-        <v>17.35584111099147</v>
+        <v>16.77353987902499</v>
       </c>
       <c r="F88">
-        <v>710.0408063565463</v>
+        <v>670</v>
       </c>
       <c r="G88">
-        <v>-13.06219454172525</v>
+        <v>-12.96983117002479</v>
       </c>
       <c r="H88">
-        <v>2.538690059220033E-34</v>
+        <v>5.281958749465102E-34</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -4507,19 +4502,19 @@
         </is>
       </c>
       <c r="D89">
-        <v>209.7499627425701</v>
+        <v>251.6488755990879</v>
       </c>
       <c r="E89">
-        <v>15.4722551405371</v>
+        <v>33.99096031013718</v>
       </c>
       <c r="F89">
-        <v>710.0029020115852</v>
+        <v>670</v>
       </c>
       <c r="G89">
-        <v>-13.55652171175926</v>
+        <v>-7.40340588506522</v>
       </c>
       <c r="H89">
-        <v>4.248905639671192E-37</v>
+        <v>7.993861001159391E-13</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4554,19 +4549,19 @@
         </is>
       </c>
       <c r="D90">
-        <v>263.2476446138537</v>
+        <v>276.1585203243752</v>
       </c>
       <c r="E90">
-        <v>15.4722551405371</v>
+        <v>19.31609360390869</v>
       </c>
       <c r="F90">
-        <v>710.0029020094565</v>
+        <v>670</v>
       </c>
       <c r="G90">
-        <v>-17.01417422494207</v>
+        <v>-14.29681000657883</v>
       </c>
       <c r="H90">
-        <v>6.287049791554419E-54</v>
+        <v>6.962686165540381E-40</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4601,19 +4596,19 @@
         </is>
       </c>
       <c r="D91">
-        <v>279.8833521495438</v>
+        <v>265.9788068026573</v>
       </c>
       <c r="E91">
-        <v>17.35584111099147</v>
+        <v>20.0524177597013</v>
       </c>
       <c r="F91">
-        <v>710.0408063561763</v>
+        <v>670</v>
       </c>
       <c r="G91">
-        <v>-16.12617621696787</v>
+        <v>-13.26417641952315</v>
       </c>
       <c r="H91">
-        <v>1.322325006817293E-49</v>
+        <v>2.404412285126871E-35</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
